--- a/data/trans_orig/P37C2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son seguras en 2023</t>
+          <t>Población según la creencia de que las vacunas son seguras en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>921</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2946</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>921</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3284</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67997</t>
+          <t>69770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71091</t>
+          <t>70139</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106500</t>
+          <t>106439</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59430</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88439</t>
+          <t>89039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95720</t>
+          <t>96747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>127894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163701</t>
+          <t>163858</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203983</t>
+          <t>204215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367368</t>
+          <t>364226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400593</t>
+          <t>400916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556676</t>
+          <t>553433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>593769</t>
+          <t>592931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934470</t>
+          <t>934812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987469</t>
+          <t>983867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,44 +1432,44 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7754</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16034</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7754</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16490</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>24574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51174</t>
+          <t>51753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81350</t>
+          <t>84354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154423</t>
+          <t>154727</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>58629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>104726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>161569</t>
+          <t>163947</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>245993</t>
+          <t>246880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>315797</t>
+          <t>327554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542252</t>
+          <t>545321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>387215</t>
+          <t>382522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>657181</t>
+          <t>659608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>773526</t>
+          <t>796184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1147137</t>
+          <t>1151999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1563819</t>
+          <t>1561833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1868720</t>
+          <t>1843001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1485845</t>
+          <t>1491349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1768855</t>
+          <t>1769281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3109779</t>
+          <t>3109017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3523885</t>
+          <t>3512460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>33472</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64583</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124796</t>
+          <t>123671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>168894</t>
+          <t>169589</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>108778</t>
+          <t>107606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143922</t>
+          <t>143690</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243827</t>
+          <t>242859</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>301215</t>
+          <t>298716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>442760</t>
+          <t>443924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>490793</t>
+          <t>490874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>485601</t>
+          <t>487002</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>524383</t>
+          <t>524806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>940556</t>
+          <t>941745</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1003399</t>
+          <t>1003902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36741</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>52192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>73923</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>143901</t>
+          <t>145546</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>217605</t>
+          <t>223027</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121374</t>
+          <t>123946</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181659</t>
+          <t>181025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>286356</t>
+          <t>286923</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>381517</t>
+          <t>389503</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>514940</t>
+          <t>541765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>758429</t>
+          <t>765330</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>632648</t>
+          <t>615526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>917021</t>
+          <t>901003</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1236432</t>
+          <t>1227200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1598289</t>
+          <t>1598166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2414971</t>
+          <t>2410322</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2714253</t>
+          <t>2696182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2553986</t>
+          <t>2568943</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2847523</t>
+          <t>2863586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5046726</t>
+          <t>5048488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5467746</t>
+          <t>5476762</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Estudios-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>969</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>969</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>44045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49270</t>
+          <t>59379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49091</t>
+          <t>49561</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38733</t>
+          <t>41016</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69770</t>
+          <t>62409</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>85398</t>
+          <t>93605</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>76883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106439</t>
+          <t>110251</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72959</t>
+          <t>85877</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>69091</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89039</t>
+          <t>103199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>110357</t>
+          <t>124091</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96747</t>
+          <t>109071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127894</t>
+          <t>143012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>183316</t>
+          <t>209968</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163858</t>
+          <t>186859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204215</t>
+          <t>233517</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>384494</t>
+          <t>421431</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364226</t>
+          <t>399926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400916</t>
+          <t>442133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>577323</t>
+          <t>629637</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553433</t>
+          <t>609474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>592931</t>
+          <t>646610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>961817</t>
+          <t>1051068</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934812</t>
+          <t>1022302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983867</t>
+          <t>1077046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,49%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>504054</t>
+          <t>562075</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>504054</t>
+          <t>562075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>504054</t>
+          <t>562075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>743200</t>
+          <t>810156</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>743200</t>
+          <t>810156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>743200</t>
+          <t>810156</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1247254</t>
+          <t>1372231</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1247254</t>
+          <t>1372231</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1247254</t>
+          <t>1372231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,67 +1442,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16034</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>15168</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>8406</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>26278</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>14584</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7957</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>26211</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>42874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,27 +1555,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>41013</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24574</t>
+          <t>29001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>54619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122602</t>
+          <t>138489</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>114427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154727</t>
+          <t>168430</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81945</t>
+          <t>93767</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>74018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104726</t>
+          <t>114386</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>204547</t>
+          <t>232256</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>163947</t>
+          <t>199888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>246880</t>
+          <t>268660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>465776</t>
+          <t>518384</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327554</t>
+          <t>475452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>545321</t>
+          <t>567928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>495969</t>
+          <t>480851</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382522</t>
+          <t>448331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>659608</t>
+          <t>518202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>961745</t>
+          <t>999235</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>796184</t>
+          <t>942258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1151999</t>
+          <t>1062169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1656202</t>
+          <t>1521200</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1561833</t>
+          <t>1468057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1843001</t>
+          <t>1568956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1634659</t>
+          <t>1569121</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1491349</t>
+          <t>1530177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1769281</t>
+          <t>1606404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3290861</t>
+          <t>3090321</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3109017</t>
+          <t>3023096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3512460</t>
+          <t>3152457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2276003</t>
+          <t>2213530</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2276003</t>
+          <t>2213530</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2276003</t>
+          <t>2213530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2231877</t>
+          <t>2164462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2231877</t>
+          <t>2164462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2231877</t>
+          <t>2164462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4507880</t>
+          <t>4377993</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4507880</t>
+          <t>4377993</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4507880</t>
+          <t>4377993</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2202,27 +2202,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39072</t>
+          <t>40926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>37576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>52618</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62429</t>
+          <t>69479</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>145499</t>
+          <t>165476</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123671</t>
+          <t>142432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169589</t>
+          <t>192086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>125000</t>
+          <t>139633</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107606</t>
+          <t>120675</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143690</t>
+          <t>159016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>270499</t>
+          <t>305109</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>242859</t>
+          <t>277209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>298716</t>
+          <t>338023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>467888</t>
+          <t>510375</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>443924</t>
+          <t>482291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>490874</t>
+          <t>535205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>506365</t>
+          <t>561439</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>487002</t>
+          <t>540265</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>524806</t>
+          <t>580746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>974253</t>
+          <t>1071815</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941745</t>
+          <t>1036197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1003902</t>
+          <t>1102519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658674</t>
+          <t>732992</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658674</t>
+          <t>732992</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658674</t>
+          <t>732992</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1305297</t>
+          <t>1444579</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1305297</t>
+          <t>1444579</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1305297</t>
+          <t>1444579</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,69 +2771,69 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>13024</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7292</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>23082</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>11195</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>5559</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>21283</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35793</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>30450</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52192</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>64404</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>50616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73923</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>184619</t>
+          <t>210190</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>145546</t>
+          <t>178651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>223027</t>
+          <t>247376</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>168289</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123946</t>
+          <t>146165</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181025</t>
+          <t>193235</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>337550</t>
+          <t>378479</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>286923</t>
+          <t>341451</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>389503</t>
+          <t>421857</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>684235</t>
+          <t>769738</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>541765</t>
+          <t>717355</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>765330</t>
+          <t>823544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>731326</t>
+          <t>744575</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>615526</t>
+          <t>701195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>901003</t>
+          <t>787141</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1415561</t>
+          <t>1514313</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1227200</t>
+          <t>1446798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1598166</t>
+          <t>1581245</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2508584</t>
+          <t>2453007</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2410322</t>
+          <t>2391895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2696182</t>
+          <t>2510934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2718346</t>
+          <t>2760197</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2568943</t>
+          <t>2708865</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2863586</t>
+          <t>2805296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5226931</t>
+          <t>5213204</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5048488</t>
+          <t>5138691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5476762</t>
+          <t>5293491</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3426680</t>
+          <t>3487193</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3426680</t>
+          <t>3487193</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3426680</t>
+          <t>3487193</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3633750</t>
+          <t>3707610</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3633750</t>
+          <t>3707610</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3633750</t>
+          <t>3707610</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7060431</t>
+          <t>7194803</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7060431</t>
+          <t>7194803</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7060431</t>
+          <t>7194803</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
